--- a/venn_proteins.xlsx
+++ b/venn_proteins.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -32,7 +32,7 @@
     <t xml:space="preserve">DiFi_2D_UC</t>
   </si>
   <si>
-    <t xml:space="preserve">AAMP, ABCE1, ABR, ABRAXAS2, ACAA1, ACP1, ACP3, ACTL6A, ACTR10, ADAM9, ADH1C, ADK, AGO2, AHCYL1, ALDH1B1, ALDH2, ANP32E, ANT3, ANXA4, AP1G2, AP1S1, AP2A1, AP2M1, AP3D1, ARFIP1, ARHGAP12, ARHGEF16, ARMH3, ARRB1, ASPSCR1, ATG7, ATP6AP2, ATP6V1B2, ATP6V1E1, ATXN10, B3GALT6, B3GAT3, B3GNT3, B4GALT4, BABAM2, BAZ1B, BCCIP, BLOC1S6, BMP4, BOLA2, BRCC3, C1GALT1C1, C9orf64, CA11, CA12, CALU, CBSL, CCAR1, CCL24, CCN2, CCNL1, CCT3, CD2AP, CDK5RAP3, CFAP20, CHID1, CIAO1, CLIC4, CLPB, CLTA, CLUH, CMAS, CNOT9, CNP, COPG2, COPS2, COPS4, COPS5, COPS6, COPS7A, COPS7B, COPS8, CORO1A, CPNE1, CPNE3, CPSF2, CPSF3, CPSF6, CPSF7, CSF2RA, CSNK1A1, CTBP1, CTBP2, CTNNBL1, CTPS1, CTPS2, CTSF, CUL1, CUL2, CUL3, CUL4A, CUL4B, CUL5, CYFIP1, DARS1, DAZAP1, DCBLD1, DCUN1D1, DDB2, DDX17, DDX19A, DDX21, DDX23, DDX39A, DDX3X, DDX5, DEK, DENR, DHX15, DHX36, DIAPH2, DIEXF, DIS3, DNAJA1, DNAJA2, DNAJB11, DNAJC3, DNM2, DYNC1H1, DYNC1LI1, DYNLT1, ECHDC1, ECPAS, EFL1, EFTUD2, EHD1, EIF1AX, EIF2A, EIF2B1, EIF2B3, EIF3A, EIF3D, EIF3E, EIF3F, EIF3H, EIF3M, EIF4A3, ELP2, ELP4, ELP6, EMG1, EML3, ENGASE, ENTPD5, ENTPD6, EPHB1, EPPK1, EPS8L2, ERH, EXOSC4, EXOSC7, EXOSC8, EXOSC9, F5, FAM171A1, FAM20B, FAM3C, FAM83B, FARSB, FAT1, FBXL8, FCGRT, FEN1, FERMT1, FGFBP1, FLII, FNBP1L, FRYL, FUBP1, FURIN, FUT2, GALK2, GATD3B, GCNT1, GEMIN5, GET3, GIT1, GLCE, GLMN, GLYR1, GMFB, GMPPB, GMPS, GNE, GOLPH3, GORASP2, GPA33, GPD1L, GPS1, GRWD1, GSTK1, GTF3C4, H1.4, H1.5, HAT1, HDLBP, HEATR5B, HINT2, HNRNPDL, HNRNPH2, HS6ST2, HSD17B4, HSPA14, HTATIP2, IARS1, IARS2, IMPA2, IMPDH2, INF2, INPP1, INPP4B, INPPL1, INTS13, INTS3, ITPA, JMJD1C, KCNAB2, KHSRP, KIAA0319L, KIF23, KL, KLC1, KLK10, KLK11, KPNA2, KPNA6, KRT23, L1RE1, LAMTOR2, LANCL1, LARGE2, LARP1, LCN2, LFNG, LIPG, LNX2, LRP6, LRP8, LRRC59, LUC7L2, LYPLAL1, LYSC, MACROH2A2, MAN1A2, MAPKAPK3, MBTPS1, MCM2, MCM3, MCM4, MCM5, MCM6, MCTS1, MEMO1, MFAP2, MGAT3, MGAT4B, MLEC, MMP14, MRI1, MRTO4, MTMR12, MTREX, MYL6B, MYO18A, MYO6, NAA10, NAA20, NAAA, NADSYN1, NAPA, NAXD, NCOA5, NDRG3, NELFB, NELFCD, NIPSNAP1, NOL11, NOLC1, NOP58, NPM3, NRCAM, NTN4, NUDT19, NUDT2, NUP133, NUP155, NUP37, NUP54, NUP58, NUP62, NUP88, NXF1, OAF, OGFOD1, OPA1, OPLAH, PACSIN3, PAPOLA, PAPSS1, PARD3, PCDH19, PCID2, PCOLCE2, PDCD4, PDE12, PEF1, PHF5A, PHPT1, PIK3R1, PKDCC, PKP2, PLA2G2A, PLA2R1, PLAA, PLRG1, PMM2, POF1B, POLA1, POLR2E, POR, PPAT, PPCS, PPIH, PPL, PPM1A, PPP1R12A, PPP4R3A, PRKAG1, PRPF19, PRPF4, PRPF40A, PRPF4B, PRPF8, PSMC2, PSMD13, PSMD4, PSMD5, PSMD9, PSME4, PSPC1, PSTPIP2, PTK2, PTPN23, PTPN6, PWP1, PXYLP1, PYCR1, RAB14, RAB3GAP1, RABGAP1, RABGGTA, RAD21, RAE1, RANGAP1, RARRES1, RAVER1, RBBP5, RBX1, RCC1, RECQL, RELA, REPIN1, RFNG, RHOC, RIOX2, RNASE6, RPA1, RPA3, RPL17, RPL19, RPL21, RPL29, RPL3, RPL30, RPL34, RPL35, RPL5, RPL6, RPL7, RPS11, RPS13, RPS14, RPS18, RPS23, RPS24, RPS27, RPS3A, RPS6, RPS6KA3, RPS9, RPUSD2, RRP9, RSPRY1, RTCB, RTRAF, SAP18, SARS1, SATB1, SBDS, SCFD1, SCLY, SEC16A, SEC24A, SEC24B, SEH1L, SEMA3C, SEMA3G, SEPHS2, SEPTIN10, SERPIND1, SERPINI1, SETD3, SF3B1, SHMT2, SHPK, SLC9A3R1, SLPI, SMARCE1, SMC3, SMU1, SNU13, SNX1, SORL1, SRC, SRM, SRP72, SRPK1, SRPK2, SRRT, SRSF1, SRSF2, SRSF3, SRSF6, SRSF7, SSRP1, ST3GAL4, STAG1, STX3, SUCLG2, SUPT6H, SWAP70, SYMPK, TBCB, TBL1XR1, TCN2, TEP1, TGFB1, THAP12, THOC2, THOC3, THOC5, TIMP3, TIMP4, TJP2, TMOD3, TNFSF15, TNPO2, TOMM70, TOP1, TOR1B, TRA2B, TRABD2A, TRIM2, TRIM21, TRIM25, TRIM28, TRMT1, TRMT6, TSKU, U2AF1L5, U2SURP, UBE2Z, UBE3A, UBE4A, UBR4, UCHL3, UCHL5, UFL1, UNC45A, UPF2, USP39, UXS1, VARS1, VIRMA, VPS25, VPS45, VPS4B, VPS52, VTA1, VWA2, WDR12, WDR43, WDR48, WDR61, WDR77, WDR82, XPO5, XPOT, YES1, ZNF207</t>
+    <t xml:space="preserve">AAMP, ABCE1, ABR, ABRAXAS2, ACAA1, ACP1, ACP3, ACTL6A, ACTR10, ADAM9, ADH1C, ADK, AGO2, AHCYL1, ALDH1B1, ALDH2, ANP32E, ANT3, AP1G2, AP1S1, AP2A1, AP2A2, AP2M1, AP2S1, AP3D1, ARFIP1, ARHGAP12, ARHGEF16, ARMH3, ARRB1, ASPH, ASPSCR1, ATG7, ATP6AP2, ATP6V1B2, ATP6V1E1, ATXN10, B3GALT6, B3GAT3, B3GNT3, B4GALT4, BABAM2, BAZ1B, BCCIP, BLOC1S6, BMP4, BOLA2, BRCC3, C1GALT1C1, C1R, C4B, C9orf64, CA11, CA12, CALU, CBSL, CCAR1, CCL24, CCN2, CCNL1, CD2AP, CDK5RAP3, CEMIP, CFAP20, CHID1, CIAO1, CLIC4, CLPB, CLTA, CLU, CLUH, CMAS, CNOT9, CNP, COPG2, COPS2, COPS4, COPS5, COPS6, COPS7A, COPS7B, COPS8, CPNE1, CPNE3, CPSF2, CPSF3, CPSF6, CPSF7, CSF2RA, CSNK1A1, CTBP1, CTBP2, CTNNBL1, CTPS1, CTPS2, CTSF, CUL1, CUL2, CUL3, CUL4A, CUL4B, CUL5, CYFIP1, DARS1, DAZAP1, DCBLD1, DCUN1D1, DDB2, DDX17, DDX19A, DDX21, DDX23, DDX3X, DDX5, DEK, DENR, DHX15, DHX36, DIAPH2, DIEXF, DIS3, DNAJA1, DNAJA2, DNAJB11, DNAJC3, DNM2, DYNC1H1, DYNC1LI1, DYNLT1, ECHDC1, ECPAS, EFL1, EFTUD2, EHD1, EIF1AX, EIF2A, EIF2B1, EIF2B3, EIF3A, EIF3D, EIF3E, EIF3F, EIF3H, EIF3M, EIF4A3, ELP2, ELP4, ELP6, EMG1, EML3, ENGASE, ENTPD5, ENTPD6, EPHB1, EPPK1, EPS8L2, ERH, EXOSC4, EXOSC7, EXOSC8, EXOSC9, FAM171A1, FAM20B, FAM3C, FAM83B, FARSB, FAT1, FBXL8, FCGRT, FEN1, FERMT1, FGFBP1, FLII, FNBP1L, FRYL, FUBP1, FURIN, FUT2, GALK2, GATD3B, GBA, GCNT1, GEMIN5, GET3, GIT1, GLCE, GLMN, GLYR1, GMFB, GMPPB, GMPS, GNE, GOLPH3, GORASP2, GPA33, GPD1L, GPS1, GRWD1, GSTK1, GTF3C4, H1.4, H1.5, HAT1, HDLBP, HEATR5B, HINT2, HNRNPH2, HS6ST2, HSD17B4, HSPA14, HTATIP2, HTRA1, IARS1, IARS2, IGFBP3, IMPA2, INF2, INPP1, INPP4B, INPPL1, INTS13, INTS3, ITM2B, ITPA, JMJD1C, KCNAB2, KHSRP, KIAA0319L, KIF23, KL, KLC1, KLK10, KLK11, KPNA2, KPNA6, KRT23, L1RE1, LAMTOR2, LANCL1, LARGE2, LARP1, LCN2, LFNG, LIPG, LNX2, LRP6, LRP8, LRRC59, LYPLAL1, LYSC, MACROH2A2, MAN1A2, MAPKAPK3, MBTPS1, MCM2, MCM3, MCM4, MCM5, MCM6, MCTS1, MEMO1, MFAP2, MGAT3, MGAT4B, MLEC, MMP14, MRI1, MRTO4, MTMR12, MTREX, MYL6B, MYO18A, MYO6, NAA10, NAA20, NAAA, NADSYN1, NAPA, NAXD, NCOA5, NDRG3, NELFB, NELFCD, NIPSNAP1, NOL11, NOLC1, NOP58, NPM3, NRCAM, NTN4, NUDT19, NUDT2, NUP133, NUP155, NUP37, NUP54, NUP58, NUP62, NUP88, NXF1, OAF, OGFOD1, OPA1, OPLAH, PACSIN3, PAPOLA, PAPSS1, PARD3, PCDH19, PCID2, PCOLCE2, PCSK6, PDCD4, PDE12, PEF1, PHF5A, PHPT1, PIK3R1, PKDCC, PKP2, PLA2G2A, PLA2R1, PLAA, PLRG1, PMM2, POLA1, POLR2E, POR, PPAT, PPCS, PPIH, PPL, PPM1A, PPP1R12A, PPP4R3A, PRKAG1, PRPF19, PRPF4, PRPF40A, PRPF4B, PRPF8, PSMC2, PSMD13, PSMD4, PSMD5, PSMD9, PSME4, PSPC1, PSTPIP2, PTK2, PTPN23, PTPN6, PWP1, PXYLP1, PYCR1, RAB14, RAB3GAP1, RABGAP1, RABGGTA, RAD21, RAE1, RANGAP1, RARRES1, RAVER1, RBBP5, RBX1, RCC1, RECQL, RELA, REPIN1, RFNG, RIOX2, RNASE6, RPA3, RPL17, RPL19, RPL21, RPL34, RPL35, RPL5, RPL6, RPS11, RPS13, RPS16, RPS27, RPS3A, RPS6, RPS6KA3, RPUSD2, RRP9, RSPRY1, RTCB, RTN4, RTRAF, SAP18, SARS1, SATB1, SBDS, SCFD1, SCLY, SEC16A, SEC24A, SEC24B, SEH1L, SEMA3B, SEMA3C, SEMA3G, SEPHS2, SEPTIN10, SERPIND1, SERPINI1, SETD3, SF3B1, SHPK, SLC9A3R1, SLPI, SMARCE1, SMC3, SMPD1, SMU1, SNU13, SNX1, SORL1, SRC, SRM, SRP72, SRPK1, SRPK2, SRRT, SRSF3, SRSF6, SSRP1, ST3GAL4, STAG1, STX3, SUCLG2, SUPT6H, SWAP70, SYMPK, TBCB, TBL1XR1, TCN2, TEP1, TGFB1, THAP12, THOC2, THOC3, THOC5, TIMP3, TIMP4, TJP2, TMOD3, TNFSF15, TNPO2, TOMM70, TOP1, TOR1B, TRABD2A, TRIM2, TRIM21, TRIM25, TRIM28, TRMT1, TRMT6, TSKU, U2AF1L5, U2SURP, UBE2Z, UBE3A, UBE4A, UBR4, UCHL3, UCHL5, UFL1, UNC45A, UPF2, USP39, UXS1, VARS1, VIRMA, VPS25, VPS45, VPS4B, VPS52, VTA1, VWA2, WDR12, WDR43, WDR48, WDR61, WDR77, WDR82, XPO5, XPOT, YES1, ZNF207</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
@@ -41,7 +41,7 @@
     <t xml:space="preserve">DiFi_3D_UC</t>
   </si>
   <si>
-    <t xml:space="preserve">BDH2, C2CD3, CAST, CSNK2A1, KRT6B, MROH7, NAA35, NIPBL, NOTCH3, NUP160, PELP1, POLA2, PRKRA, RALY, RPS25, S100A13, TUBB3, XAB2</t>
+    <t xml:space="preserve">BDH2, C2CD3, CAST, CSNK2A1, GPC4, MROH7, NAA35, NIPBL, NOTCH3, NUP160, PELP1, POLA2, PRKRA, RALY, S100A13, TUBB3, XAB2</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
@@ -50,25 +50,16 @@
     <t xml:space="preserve">DiFi_3D_FPLC</t>
   </si>
   <si>
-    <t xml:space="preserve">ACYP1, ADA, AGFG1, AGL, ARF4, ASNS, ATP1A1, BAX, BPTF, BSG, CAH2, CARS2, CD320, CD9, CHMP1B, CLINT1, CNN3, CRELD1, CRKL, CSK, CXADR, DDX18, DYNLL1, ECE1, EIF4B, ENAH, FABP6, FAM234A, FARSA, FIS1, FKBP2, FLG2, GIPC1, GOLGA2, GRPEL1, HNMT, HTATSF1, HYI, IGLC2, KIRREL1, KNTC1, LMO7, MANF, METTL1, MIX23, MST1R, NT5E, PFKP, PGRMC1, PIN4, PLD3, POLR1B, PPIE, PPP1R14B, PSMB10, PSMB9, PSMG2, RAB3GAP2, RP2, RPL24, S100A10, SH3BGRL, SMAP1, SMC4, SMPDL3B, SPINT2, STAMBP, SUPT5H, TOP2A, TPK1, TSG101, UFM1, YKT6, ZZEF1</t>
+    <t xml:space="preserve">ACYP1, ADA, AGFG1, AGL, ARF4, ASNS, ATP1A1, BAX, BPTF, BSG, CAH2, CARS2, CD320, CD9, CHMP1B, CLINT1, CNN3, CRELD1, CRKL, CSK, CXADR, DDX18, DYNLL1, ECE1, EIF4B, ENAH, FABP6, FAM234A, FARSA, FIS1, FKBP2, GIPC1, GOLGA2, GRPEL1, HNMT, HTATSF1, HYI, KIRREL1, KNTC1, LAMB2, LMO7, MANF, METTL1, MIX23, MST1R, NT5E, PGRMC1, PIN4, PLD3, POLR1B, PPIE, PPP1CB, PPP1R14B, PSMB10, PSMB9, PSMG2, RAB3GAP2, RP2, S100A10, SH3BGRL, SMAP1, SMC4, SMPDL3B, SPINT2, STAMBP, SUPT5H, TOP2A, TPK1, TSG101, UFM1, YKT6, ZZEF1</t>
   </si>
   <si>
     <t xml:space="preserve">4</t>
   </si>
   <si>
-    <t xml:space="preserve">HNPCC_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMTS5, ANPEP, ANTXR1, ARSB, C1QTNF5, CD248, CFAP44, CFD, COL4A2, COL5A2, CPA4, CSPG4, FAM20C, FAP, FERMT2, FGB, FNDC1, GALC, GFRA1, GPC6, GPNMB, HLA class I histocompatibility antigen, A alpha chain OS=Homo sapiens OX=9606 GN=HLA-A PE=1 SV=2, IGFBP5, IGFBP6, ISLR, ITGBL1, KRT7, LOX, MATN2, MCAM, MMP1, MXRA8, NFASC, OLFML3, P3H1, PDE5A, PDGFRB, PTN, RAB21, RDX, RECK, SCPEP1, SIRPA, SNTB2, sp|CATA_HUMAN|, sp|GSTP1_HUMAN|, SPON2, TGM2, VCAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2, COL2A1, HRNR, INA, KRT6A, RPL37AP8, SERPINA7, SERPINF2, TFPI2</t>
+    <t xml:space="preserve">SAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2M, ACTA2, AFM, AFP, AGPAT1, ALB, ANO9, ANXA5, ANXA6, APCS, APOA1, APOA4, APOB, APOC2, APOC3, APOE, APOM, ARG1, ARHGDIB, ARL6IP5, ASPRV1, ATP5A1, ATP5B, ATP5J2, ATP7B, BPIFB1, BRWD3, C1S, C4A, C4BPA, C5, C9, CASP14, CAT, CCL28, CCL5, CDSN, CELA3B, CFH, CLEC3B, COL1A1, COL1A2, COL4A2, COL4A5, COL6A2, COL6A3, COMP, CPA1, CPB1, CRISPLD2, CTSD, Cytochrome c oxidase subunit 2 OS=Homo sapiens GN=MT-CO2 PE=1 SV=1, DCD, DSC1, DSG1, EEF1A1P5, EIF5AL1, F9, FBN1, FGA, FGB, FGG, GC, GMFG, GNAI2, GNLY, GSN, GZMA, GZMB, GZMM, H2AFY, H2AFZ, HBA1, HBB, HGF, HGFAC, HIF1A, HIST1H1B, HIST1H1E, HIST1H2AB, HIST1H2AG, HIST1H2BK, HIST1H4A, HIST2H3A, HLA class I histocompatibility antigen, A-2 alpha chain OS=Homo sapiens GN=HLA-A PE=1 SV=1, HLA class I histocompatibility antigen, B-7 alpha chain OS=Homo sapiens GN=HLA-B PE=1 SV=3, HLA class II histocompatibility antigen, DR alpha chain OS=Homo sapiens GN=HLA-DRA PE=1 SV=1, HNRNPCL2, HP, HPX, HRG, HRNR, HSPB1, IFNG, IGHA1, IGHG2, IGHG3, IGKC, Immunoglobulin gamma-1 heavy chain OS=Homo sapiens PE=1 SV=1, Immunoglobulin heavy variable 3-74 OS=Homo sapiens GN=IGHV3-74 PE=3 SV=1, Immunoglobulin kappa variable 2-28 OS=Homo sapiens GN=IGKV2-28 PE=3 SV=1, Immunoglobulin kappa variable 3-20 OS=Homo sapiens GN=IGKV3-20 PE=1 SV=2, Immunoglobulin kappa variable 3D-11 OS=Homo sapiens GN=IGKV3D-11 PE=3 SV=6, Immunoglobulin kappa variable 3D-7 OS=Homo sapiens GN=IGKV3D-7 PE=3 SV=5, Immunoglobulin lambda variable 1-47 OS=Homo sapiens GN=IGLV1-47 PE=1 SV=2, Immunoglobulin lambda variable 3-9 OS=Homo sapiens GN=IGLV3-9 PE=3 SV=1, Immunoglobulin lambda-1 light chain OS=Homo sapiens PE=1 SV=1, Immunoglobulin mu heavy chain OS=Homo sapiens PE=1 SV=1, ITGAL, ITIH1, ITIH2, ITIH3, ITIH4, JCHAIN, KPRP, KRT14, KRT16, KRT17, KRT5, KRT6A, KRT7, KRT77, LASP1, LCN1P1, LGALS7, LPL, LSP1, LUM, LYZ, MFGE8, MGP, MSN, MUC5B, MYL12B, PGAM2, PIP, PKN3, PRF1, PROS1, PRR4, PRSS1, PTHLH, PTPRC, PZP, RAB40C, RAC2, RAP1B, RBMXL1, RPL13AP3, RPL14, RPL18, RPL27, RPL7A, S100A8, S100A9, SEPT7, SERPINA10, SERPINA7, SERPINB12, SERPINB3, SERPINC1, SERPINF2, SERPING1, SETSIP, SHBG, SLC25A5, SNRPB, STMN1, SUMO4, TEKT1, TF, TGM3, THBS4, TMEM109, TMOD2, TMSB4X, TOMM7, UBE2NL, VCAM1, VDAC1, VDAC2, VIM, VNN1, XCL2, ZNFX1</t>
   </si>
   <si>
     <t xml:space="preserve">1/2</t>
@@ -77,7 +68,7 @@
     <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_UC</t>
   </si>
   <si>
-    <t xml:space="preserve">AARS1, ABHD10, ACTR1A, ADAR, ADSL, AK1, ATF6B, ATP5F1B, BAG1, BAG6, CCAR2, CCDC6, CCT7, CDHR1, CGN, CLIP1, CLYBL, COL17A1, COPB1, CRIM1, CTNNB1, DIAPH1, EIF2S3, EIF3I, EIF5, EPHX2, EPS15, EXOSC2, FRAS1, GALNT18, GALNT5, GART, IPO4, KDM1A, KPNA1, KRT78, LRBA, LSM4, METAP2, MPRIP, MTHFD1, NAP1L1, NIT1, NMT1, NOMO3, NONO, NOTCH1, NRBP1, NRXN3, NT5C, NUP210, OXSM, PACSIN2, PAK2, PFKL, PRMT5, PSMC3, PSMC6, PSMD1, PSMG1, RAB10, RAB1B, RAB7A, RANBP1, RAP1GDS1, RCN1, RPA2, RPL38, RPLP1, RPLP2, RPS10, RPS17, RPS19, RPS2, RRM1, RUVBL1, SEC31A, SEPTIN8, SEPTIN9, SHTN1, SLC39A6, SMC1A, SNRNP70, STRBP, STXBP2, SUMF2, TBC1D4, TMF1, TNPO1, USO1, VAT1, VPS29, XYLT1, ZC3H15</t>
+    <t xml:space="preserve">AARS1, ABHD10, ACTR1A, ADAR, ADSL, AK1, ATF6B, ATP5F1B, BAG1, BAG6, CCAR2, CCDC6, CDHR1, CGN, CLIP1, CLYBL, COL17A1, COPB1, CRIM1, CTNNB1, DIAPH1, EEA1, EIF2S3, EIF3B, EIF3I, EIF5, EPHX2, EPS15, EXOSC2, FRAS1, GALNT18, GALNT5, GART, GSPT1, IPO4, KDM1A, KPNA1, KTN1, LAMB1, LRBA, METAP2, MPRIP, NAP1L1, NIT1, NMT1, NOMO3, NONO, NOTCH1, NRBP1, NRXN3, NT5C, NUP210, OXSM, PACSIN2, PAK2, PFKL, PRMT5, PSMC3, PSMC6, PSMD1, PSMG1, RAB10, RAB7A, RANBP1, RAP1GDS1, RCN1, RPA2, RPL38, RPLP1, RPS17, RRM1, RUVBL1, SEC31A, SEMA5A, SEPTIN11, SEPTIN8, SEPTIN9, SHTN1, SLC39A6, SMC1A, SNRNP70, SOD3, STRBP, STXBP2, SUMF2, TBC1D4, TMF1, TNPO1, USO1, VAT1, VPS29, XYLT1, ZC3H15</t>
   </si>
   <si>
     <t xml:space="preserve">1/3</t>
@@ -86,25 +77,16 @@
     <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_FPLC</t>
   </si>
   <si>
-    <t xml:space="preserve">ABHD14B, ACBD3, ACSS2, ADAM17, ADGRG1, AFDN, AIP, AK3, AKR7A2, AP1M1, ARCN1, ARHGEF1, ARHGEF7, ARMT1, ARPC5L, ART3, B3GNT2, BLVRA, C20orf27, CASK, CBX1, CCL15, CDH1, CKAP5, CLNS1A, CNBP, CNOT1, CNPY2, CRK, CSTF1, DCBLD2, DCTD, DDC, DDT, DDX42, DDX6, DKC1, DNAJC10, DNAJC9, DUT, DYM, EEF1E1, EIF2S2, EIF3G, EIF4E2, EIF5B, ELOB, ELOC, ETHE1, F11R, FUT11, FUT8, GALT, GINS4, GLRX3, GPX4, GRB2, GYG1, H2AC6, HDAC1, HDAC2, HDDC3, HDHD3, HEBP1, HGS, HLA.B, HMOX2, HNRNPA3, HNRNPH1, HNRNPL, HNRNPM, HSD17B10, HSPA13, HUWE1, IDH2, IGFBP4, IGSF8, IRF3, LACTB2, LAMTOR3, LIN7C, LMAN1, LPP, LSM3, MACROH2A1, MAGOH, MAPK1, MAPK13, MAPK3, MARS1, MATR3, MAVS, MEAK7, MGAT2, MOB1A, MOB4, MORF4L2, MTA2, MVP, NAA15, NCBP1, NCKAP1, NUCB2, OSGEP, OXSR1, PAPSS2, PARP1, PAXX, PCMT1, PCSK5, PDLIM5, PITHD1, PITPNA, PKP3, POLR2H, PPP2R5D, PPT2, PREPL, PRTFDC1, PUDP, PUF60, RAB2A, RAD23B, RBM25, RBM39, RBMX, REG1A, RMDN3, RPL23A, S100A16, SAFB, SART3, SF1, SF3B2, SF3B4, SF3B6, SHMT1, SMARCC1, SMARCC2, SMYD5, SNRNP200, SRI, SRP14, SUGT1, TATDN1, TIAL1, TPMT, TRAP1, TTC39B, TWF1, TWSG1, TXNDC12, UFD1, UPF1, VAPA, WDR5, WDR92, XYLT2, YTHDF3, ZMYND8</t>
+    <t xml:space="preserve">ABHD14B, ACBD3, ACSS2, ADAM17, ADGRG1, AFDN, AIP, AK3, AKR7A2, AP1M1, ARCN1, ARHGEF1, ARHGEF7, ARMT1, ART3, B3GNT2, BLVRA, C20orf27, CASK, CBX1, CCL15, CDH1, CKAP5, CLNS1A, CNBP, CNOT1, CNPY2, CRK, CSTF1, DCBLD2, DCTD, DDC, DDT, DDX42, DDX6, DKC1, DNAJC10, DNAJC9, DUT, DYM, EEF1E1, EIF2S2, EIF3G, EIF4E2, EIF5B, ELOB, ELOC, ETHE1, F11R, FUT11, FUT8, GALT, GINS4, GLRX3, GPX4, GRB2, GYG1, H2AC6, HDAC1, HDAC2, HDDC3, HDHD3, HEBP1, HGS, HLA.B, HMOX2, HNRNPL, HNRNPM, HSPA13, HUWE1, IDH2, IGFBP4, IGSF8, IRF3, LACTB2, LAMTOR3, LIN7C, LMAN1, LPP, LSM3, MACROH2A1, MAGOH, MAPK1, MAPK13, MAPK3, MARS1, MATR3, MAVS, MEAK7, MGAT2, MOB1A, MOB4, MORF4L2, MTA2, MVP, NAA15, NCBP1, NCKAP1, NUCB2, OSGEP, OXSR1, PAPSS2, PARP1, PAXX, PCMT1, PCSK5, PDLIM5, PITHD1, PITPNA, PKP3, PLAU, POLR2H, PPP2R5D, PPT2, PREPL, PRTFDC1, PTGR1, PUDP, PUF60, RAB2A, RAD23B, RBM25, RBM39, RBMX, REG1A, RMDN3, RPL23A, S100A16, SAFB, SART3, SF1, SF3B2, SF3B4, SF3B6, SHMT1, SMARCC1, SMARCC2, SMYD5, SNRNP200, SRI, SUGT1, TATDN1, TIAL1, TPMT, TRAP1, TTC39B, TWF1, TWSG1, TXNDC12, UFD1, UPF1, VAPA, WDR5, WDR92, XYLT2, YTHDF3, ZMYND8</t>
   </si>
   <si>
     <t xml:space="preserve">1/4</t>
   </si>
   <si>
-    <t xml:space="preserve">DiFi_2D_UC/HNPCC_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA1, AP2A2, AP2S1, ASPH, CEMIP, F2, GBA, HTRA1, IGFBP3, PCSK6, RPS16, SEMA3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_2D_UC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">DiFi_2D_UC/SAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA1, ANXA4, C3, CCT3, CORO1A, DDX39A, F2, F5, FBLN1, HNRNPDL, IMPDH2, LTF, LUC7L2, PLG, POF1B, RHOC, RPA1, RPL29, RPL3, RPL30, RPL7, RPS14, RPS18, RPS23, RPS24, RPS9, SHMT2, SRSF1, SRSF2, SRSF7, TRA2B, VTN</t>
   </si>
   <si>
     <t xml:space="preserve">2/3</t>
@@ -113,43 +95,25 @@
     <t xml:space="preserve">DiFi_3D_UC/DiFi_3D_FPLC</t>
   </si>
   <si>
-    <t xml:space="preserve">AACS, ACOT13, ACOT9, ACOX1, ACP2, ACTBL2, ADGRE5, AGMAT, AKR1C2, AKR7A3, ALDH3A1, APOH, ASMTL, CA9, CAMK2D, CD276, CEACAM7, CES1, CES2, CPD, D2HGDH, DBI, DMD, ENPP4, EPHA4, FAHD2A, FAM50A, FCGBP, FTH1, FTL, GALNT3, GCLM, GLMP, GLUD1, GTF2A2, HGD, IGSF9, IL13RA1, ISG15, ISM2, KREMEN1, KYAT1, L1CAM, LHPP, LRP4, LRRN1, LYPD3, LYPD8, ME3, METAP1, MPST, MST1, MUC2, NRP1, P4HA1, PFN2, PLIN3, PLXNA2, PLXNA3, PSMB4, PSMB5, PSMB7, PSMB8, PTER, PTPRJ, RBKS, RGMB, SEMA7A, SEZ6L2, SFRP2, SH3BGRL2, TTC38, TUFM, UBA6, VLDLR, XPNPEP3</t>
+    <t xml:space="preserve">AACS, ACOT13, ACOT9, ACOX1, ACP2, ACTBL2, ADGRE5, AGMAT, AKR1B1, AKR1C2, AKR7A3, ALDH3A1, ASMTL, CA9, CAMK2D, CAPN2, CD109, CD276, CEACAM7, CES1, CES2, CPD, D2HGDH, DBI, DMD, DPP4, ENPP4, EPHA4, FAHD2A, FAM50A, FCGBP, FSCN1, FTH1, FTL, GALNT3, GCLM, GLMP, GLUD1, GTF2A2, HGD, IGSF9, IL13RA1, ISG15, ISM2, KREMEN1, KYAT1, L1CAM, LHPP, LRP1, LRP4, LRRN1, LYPD3, LYPD8, MAN2B2, ME3, METAP1, MPST, MST1, MUC2, NRP1, P4HA1, PFN2, PLIN3, PLOD2, PLXNA2, PLXNA3, PSMB4, PSMB5, PSMB7, PSMB8, PTER, PTPRJ, RBKS, RGMB, SEMA7A, SEZ6L2, SFRP2, SH3BGRL2, TNC, TTC38, TUFM, UBA6, VLDLR, XPNPEP3</t>
   </si>
   <si>
     <t xml:space="preserve">2/4</t>
   </si>
   <si>
-    <t xml:space="preserve">DiFi_3D_UC/HNPCC_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_3D_UC/HCF_UC</t>
+    <t xml:space="preserve">DiFi_3D_UC/SAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN1, KRT6B, RPS25</t>
   </si>
   <si>
     <t xml:space="preserve">3/4</t>
   </si>
   <si>
-    <t xml:space="preserve">DiFi_3D_FPLC/HNPCC_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LGALS1, PPP1CB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_3D_FPLC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNPCC_UC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A2M, ADAMTS1, AFP, AGT, ANGPTL2, ANXA6, APOB, BMP1, C1S, CCDC80, CFH, CLEC11A, COL12A1, COL14A1, COL18A1, COL1A1, COL1A2, COL3A1, COL4A1, COL5A1, COL6A2, COL6A3, CPQ, CSF1, CTHRC1, CTSK, CTSL, DCN, DKK3, EFEMP1, EFEMP2, EMILIN1, FBLN2, FBLN5, FBN1, FBN2, FLNC, FMOD, FSTL1, GC, GPX3, HGF, HGFAC, HSPB1, IGFBP7, IL6ST, ITIH2, ITIH3, KRT14, KRT5, LAMA2, LAMA4, LOXL2, LUM, MAN1A1, MASP1, MFGE8, MMP2, MMP3, MRC2, MSN, MYH10, NEO1, NID1, NID2, PAMR1, PCOLCE, PLAT, PODN, PRNP, PROS1, PSG4, PTX3, PXDN, SERPINE1, SERPING1, SFRP1, sp|ALBU_BOVIN|, sp|ANT3_HUMAN|, sp|ANXA5_HUMAN|, sp|B2MG_HUMAN|, sp|CATD_HUMAN|, sp|CYC_HUMAN|, sp|GELS_HUMAN|, sp|K1C10_HUMAN|, sp|PRDX1_HUMAN|, sp|TRYP_PIG|, SPARC, SRPX, SVEP1, THBS2, THY1, TIMP2, TNFRSF11B, TPM2, VASN, VCAM1, VIM</t>
+    <t xml:space="preserve">DiFi_3D_FPLC/SAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLG2, IGLC2, LGALS1, PFKP, RPL24</t>
   </si>
   <si>
     <t xml:space="preserve">1/2/3</t>
@@ -158,133 +122,43 @@
     <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_UC/DiFi_3D_FPLC</t>
   </si>
   <si>
-    <t xml:space="preserve">ABHD11, ABRACL, ACAA2, ACE2, ACLY, ACO2, ACOT2, ACOT7, ACY1, ADAM10, ADAM15, ADD1, ADD3, ADGRL1, ADPGK, ADPRS, ADSS2, AGR2, AHCY, AHNAK, AHSA1, AIFM1, AIMP1, AIMP2, AK2, AKR1B10, AKR1C1, AKR1C3, ALDH7A1, ALDH9A1, ALYREF, AMACR, AMIGO2, ANP32A, ANP32B, ANXA3, AOC1, AP1B1, AP1M2, APEH, APEX1, API5, APPL1, APRT, ARF3, ARHGDIA, ARPC5, ASL, ASS1, ATIC, ATP6V1A, AZGP1, B2MG, B4GALT3, B4GALT5, BAG5, BCAM, BCAT2, BIN1, BIRC6, BLMH, BLVRB, BPNT1, BROX, BTF3, BTF3L4, BUB3, BZW1, BZW2, C11orf54, C11orf68, C1RL, CAB39, CAB39L, CACYBP, CAD, CADM4, CALM1, CANT1, CANX, CAP1, CAPG, CAPNS1, CAPRIN1, CAPZA1, CARM1, CASP3, CASP6, CATA, CATD, CBR1, CBX3, CCT2, CCT4, CCT6A, CCT8, CD46, CD55, CDC37, CDC42, CDCP1, CDH17, CEACAM1, CEACAM5, CEACAM6, CFL1, CHD4, CHMP4B, CHORDC1, CKB, CKMT1A, CLIC1, CLSTN2, CLSTN3, CMPK1, COCH, COMT, COPA, COPE, COPG1, COPS3, CORO1B, CPOX, CRELD2, CRYL1, CRYZ, CS, CSE1L, CST3, CST7, CSTB, CSTF3, CTH, CTNNA1, CTSH, CTSS, CTSV, CUTA, CUTC, CXCL16, CYC, CYRIB, DCPS, DCTN1, DCTPP1, DCXR, DDAH1, DDAH2, DDR1, DDX1, DHPS, DHX9, DIABLO, DLG1, DNAJC8, DNASE1, DNM1L, DNPEP, DNPH1, DPEP1, DPP9, DRAP1, DRG1, DSC2, DSG2, DSP, DSTN, DTD1, ECH1, ECI1, EEF1B2, EEF1D, EFHD2, EFNA1, EFNB1, EFNB2, EGFR, EIF2S1, EIF3C, EIF3J, EIF3K, EIF3L, EIF4A1, EIF4A2, EIF4E, EIF4G1, EIF4G2, EIF5A, EIF6, ELAVL1, EML2, EML4, ENO2, ENOPH1, ENOSF1, EPB41L2, EPCAM, EPHA1, EPHA2, EPHB2, EPHB3, EPHB4, EPRS1, ERBB2, ERBB3, ERP29, ERP44, ESD, ESRP1, ETF1, EWSR1, EXTL2, FABP1, FABP5, FAHD1, FASN, FBP1, FDPS, FGFR4, FH, FKBP1A, FKBP3, FKBP4, FLRT3, FNTA, FNTB, FSTL3, FTO, FUS, G3BP1, G3BP2, GAA, GALE, GALM, GALNT1, GALNT10, GALNT12, GALNT2, GALNT4, GALNT6, GALNT7, GANAB, GCHFR, GCLC, GDA, GDF15, GELS, GFPT1, GFUS, GGCT, GGPS1, GLA, GLO1, GLOD4, GLUL, GM2A, GMDS, GMPR2, GNPNAT1, GOLGB1, GOLM1, GPHN, GPX2, GRHPR, GSTM3, GSTP1, GUSB, GXYLT1, H2AC11, H2AX, H2AZ2, H2BC21, H2BC4, H3.3A, H3C15, H4C1, H6PD, HADH, HCFC1, HDGF, HDHD2, HEBP2, HEPH, HIBADH, HIBCH, HINT1, HIP1R, HK1, HK2, HLA.A, HLA.C, HMBS, HMGA1, HMGB1, HMGB2, HMGB3, HMGCS1, HNRNPA1, HNRNPA2B1, HNRNPAB, HNRNPC, HNRNPD, HNRNPF, HNRNPK, HNRNPR, HNRNPU, HNRNPUL1, HNRNPUL2, HPRT1, HSPA1A, HSPA4, HSPA9, HSPBP1, HSPD1, HSPE1, HSPH1, HTRA2, HYOU1, IAH1, ICOSLG, IDE, IDH1, IDI1, IFI30, IFI35, IL1R2, IMMT, IMPA1, IPO5, IPO9, IRGQ, ISOC2, IST1, ITGA6, ITGB4, JAG1, JMJD7, JUP, KHDRBS1, KHK, KLK1, KLK6, KPNA3, KPNA4, KRT10, KRT18, KRT19, KRT20, KRT8, KYAT3, LAMB3, LAMC2, LANCL2, LAP3, LCP1, LGALS4, LMNB1, LMNB2, LNPEP, LSAMP, LSM2, LSM6, LSR, LTBP1, LY75, LYPLA1, LYPLA2, MAN1B1, MANSC1, MAPK14, MAPRE1, MAT2A, MAT2B, MDK, ME2, MELTF, MET, MIF, MME, MMP15, MSLN, MTAP, MUC13, MYDGF, MYG1, MYH14, MYL12A, NAA25, NACA, NAE1, NAGA, NAGK, NANS, NAP1L4, NAPRT, NASP, NAXE, NCR3LG1, NCSTN, NDRG1, NECTIN1, NECTIN2, NECTIN3, NECTIN4, NEDD8, NEU1, NHEJ1, NHLRC2, NHLRC3, NIF3L1, NIPSNAP3A, NISCH, NIT2, NLN, NPEPL1, NPLOC4, NPNT, NQO1, NRDC, NSFL1C, NT5DC1, NTRK2, NUCKS1, NUDC, NUDCD1, NUDT14, NUDT21, NUDT5, NUMA1, NUP214, NUTF2, OLFM4, OSBP, OTUB1, PA2G4, PABPC4, PAFAH1B1, PAFAH1B2, PAFAH1B3, PAICS, PAIP1, PAK1, PALD1, PARK7, PBDC1, PCBD1, PCBP1, PCBP2, PCDH1, PCNA, PCSK9, PCYT2, PDCD10, PDCD6, PDCD6IP, PDIA5, PDXK, PFAS, PFDN1, PFDN2, PFDN5, PFDN6, PGK1, PGLS, PGM2L1, PGM3, PGP, PICALM, PIR, PITPNB, PLAUR, PLBD1, PLCB3, PLPBP, PLS1, PLXNA1, PLXNB1, PM20D2, PNPO, PODXL2, POFUT1, PPA1, PPA2, PPIA, PPID, PPIL1, PPM1B, PPM1G, PPME1, PPP1CA, PPP1R7, PPP2CA, PPP2R1A, PPP2R2A, PPP4C, PPP5C, PPP6C, PPP6R3, PPT1, PRDX1, PRDX3, PRDX5, PRKACA, PRKAR2A, PRMT1, PRPS2, PRRC1, PRSS2, PRSS22, PRSS8, PSAT1, PSMA1, PSMA2, PSMA3, PSMA4, PSMA5, PSMB1, PSMB2, PSMB6, PSMD2, PSMD3, PSMD7, PSMD8, PSME1, PSME2, PSME3, PSPH, PTBP1, PTGES3, PTMA, PTPA, PTPN11, PTPRD, PTPRF, PTPRG, PURA, PURB, PUS7, PVR, PYGL, QARS1, QDPR, QPCT, QPRT, QSOX2, RAB11B, RAB1A, RAB6A, RABL6, RAC1, RACK1, RAN, RANBP3, RARS1, RBBP4, RBBP7, RBBP9, RBM8A, RCC2, REN, REXO2, RHOA, RIDA, RNASE1, RNASE4, RNH1, RPE, RPIA, RPL11, RPL12, RPL22, RPN2, RPRD1B, RPS12, RPS20, RPS28, RPS3, RPS5, RPS7, RPSA, RRBP1, RRM2, RRP12, RSU1, S100A11, S100A4, S100A6, S100P, SAE1, SCRN1, SCYL2, SDC1, SDF4, SDHA, SEC23A, SEC23B, SEC23IP, SEC24C, SELENBP1, SELENOF, SEMA4B, SEMA4C, SEMA4D, SEMA4G, SEMA6A, SEPHS1, SERPINA1, SERPINB5, SF3A1, SF3A2, SF3A3, SF3B3, SFN, SFPQ, SGTA, SH3BGRL3, SIL1, SKP1, SLC39A10, SLC3A2, SMOC1, SMOC2, SMS, SND1, SNRPB2, SNRPD2, SNRPD3, SNRPE, SNRPF, SNRPGP15, SNRPN, SORD, SORT1, SPINT1, SPR, SRP9, SSB, SSBP1, ST13, ST14, ST6GAL1, STAG2, STARD10, STAU1, STIP1, STK24, STRAP, STRN, SUB1, SUMO2, SUPT16H, SYNCRIP, SYNE2, TAGLN2, TBCA, TCEA1, TCN1, TCP1, TES, TFG, TFRC, TGFBR3, THOP1, THUMPD1, TIMM13, TINAGL1, TIPRL, TK1, TKFC, TMEM132A, TNFRSF1B, TNFRSF21, TNPO3, TPP2, TPR, TPT1, TRIP10, TRIP11, TRNT1, TSNAX, TTLL12, TTN, TTN.1, TUBA1C, TUBA4A, TUBB4A, TWF2, TXNDC17, TXNL1, TXNRD2, TYRO3, U2AF2, UAP1, UBA2, UBA3, UBE2D3, UBE2I, UBE2K, UBE2L3, UBE2M, UBE2N, UBE2V1, UBE2V2, UBLCP1, UBQLN1, UFC1, UGDH, UGP2, USP14, USP5, USP7, VASP, VBP1, VEGFA, VIL1, VPS26A, VSNL1, XPNPEP1, XPO1, XRCC5, XRCC6, XRN2, YARS1, YBX1, ZFR</t>
+    <t xml:space="preserve">ABHD11, ACAA2, ACAT2, ACE2, ACLY, ACO1, ACO2, ACOT2, ACOT7, ACTC1, ACTN1, ACTR2, ACY1, ADAM10, ADAM15, ADD1, ADD3, ADGRL1, ADH5, ADPGK, ADPRS, ADSS2, AGA, AGR2, AGRN, AHSA1, AIFM1, AIMP1, AIMP2, AK2, AKR1A1, AKR1B10, AKR1C1, AKR1C3, ALAD, ALCAM, ALDH1A1, ALDH7A1, ALDH9A1, ALYREF, AMACR, AMIGO2, ANXA3, AOC1, AP1B1, AP1G1, AP1M2, AP2B1, APEH, APEX1, API5, APLP2, APP, APPL1, APRT, ARF3, ARHGAP1, ARPC1A, ARPC3, ARSA, ASAH1, ASL, ASS1, ATP6V1A, ATRN, AZGP1, B2MG, B4GALT1, B4GALT3, B4GALT5, B4GAT1, BAG5, BCAM, BCAT2, BIN1, BIRC6, BLVRB, BPNT1, BROX, BTD, BTF3L4, BUB3, BZW1, BZW2, C11orf54, C11orf68, C1RL, CAB39, CAB39L, CACYBP, CAD, CADM4, CAND1, CANT1, CANX, CAPN1, CAPRIN1, CAPZA1, CARM1, CARS1, CASP3, CASP6, CATA, CATD, CBR1, CBX3, CCT4, CCT5, CD44, CD46, CD55, CDC37, CDCP1, CDH17, CEACAM1, CEACAM5, CEACAM6, CFB, CHD4, CHMP4B, CHORDC1, CKB, CKMT1A, CLN5, CLSTN1, CLSTN2, CLSTN3, CMPK1, CNDP2, COCH, COMT, COPA, COPB2, COPE, COPG1, COPS3, CORO1B, CORO1C, CPOX, CPPED1, CREG1, CRELD2, CRYL1, CRYZ, CS, CSE1L, CST3, CST7, CSTB, CSTF3, CTBS, CTH, CTNNA1, CTSA, CTSB, CTSC, CTSH, CTSS, CTSV, CTSZ, CUTA, CUTC, CXCL16, CYC, CYRIB, DAG1, DCPS, DCTN1, DCTPP1, DCXR, DDAH1, DDAH2, DDB1, DDR1, DDX1, DDX39B, DHPS, DHX9, DIABLO, DLD, DLG1, DNAJC8, DNASE1, DNASE2, DNM1L, DNPEP, DNPH1, DPEP1, DPP3, DPP7, DPP9, DPYSL2, DRAP1, DRG1, DSC2, DSG2, DSTN, DTD1, ECI1, ECM1, EEF1A1, EEF1B2, EFHD2, EFNA1, EFNB1, EFNB2, EGFR, EIF2S1, EIF3C, EIF3J, EIF3K, EIF3L, EIF4A2, EIF4E, EIF4G1, EIF4G2, EIF5A, EIF6, ELAVL1, EML2, EML4, ENO2, ENOPH1, ENOSF1, EPB41L2, EPCAM, EPDR1, EPHA1, EPHA2, EPHB2, EPHB3, EPHB4, EPRS1, ERAP1, ERAP2, ERBB2, ERBB3, ERO1A, ERP29, ERP44, ESD, ESRP1, ETF1, EWSR1, EXT1, EXT2, EXTL2, EZR, FABP1, FAH, FAHD1, FASN, FBP1, FDPS, FGFR4, FH, FKBP10, FKBP1A, FKBP3, FKBP4, FKBP9, FLNB, FLRT3, FNTA, FNTB, FSTL3, FTO, FUCA1, FUCA2, FUS, G3BP1, G3BP2, GAA, GALE, GALM, GALNS, GALNT1, GALNT10, GALNT12, GALNT2, GALNT4, GALNT6, GALNT7, GARS1, GAS6, GBE1, GCHFR, GCLC, GDA, GDF15, GDI1, GELS, GFPT1, GFUS, GGH, GGPS1, GLA, GLB1, GLG1, GLO1, GLOD4, GLUL, GM2A, GMDS, GMPR2, GNPDA1, GNPDA2, GNPNAT1, GNPTG, GNS, GOLGB1, GOLM1, GOT1, GOT2, GPC1, GPHN, GPX2, GRHPR, GRN, GSR, GSS, GSTM3, GUSB, GXYLT1, H2AC11, H2AX, H2AZ2, H2BC21, H2BC4, H3.3A, H3C15, H4C1, H6PD, HADH, HARS1, HCFC1, HDGF, HDHD2, HEBP2, HEPH, HEXA, HEXB, HIBADH, HIBCH, HINT1, HIP1R, HK2, HLA.A, HLA.C, HMBS, HMGA1, HMGB3, HMGCS1, HNRNPD, HNRNPR, HNRNPUL1, HNRNPUL2, HPRT1, HSPA1A, HSPA4, HSPBP1, HSPG2, HSPH1, HTRA2, HYOU1, IAH1, ICOSLG, IDE, IDH1, IDI1, IDUA, IFI30, IFI35, IL1R2, ILF2, ILF3, IMMT, IMPA1, IPO5, IPO7, IPO9, IQGAP1, IRGQ, ISOC1, ISOC2, IST1, ITGA6, ITGB4, JAG1, JMJD7, KARS1, KHDRBS1, KHK, KIF5B, KLK1, KLK6, KPNA3, KPNA4, KPNB1, KRT19, KRT20, KYAT3, LAMA3, LAMA5, LAMB3, LAMC1, LAMC2, LAMP1, LAMP2, LANCL2, LAP3, LDLR, LGALS3, LGALS3BP, LGALS4, LGMN, LIPA, LMAN2, LMNA, LMNB2, LNPEP, LSAMP, LSM2, LSM6, LSR, LTA4H, LTBP1, LTBP4, LY75, LYPLA1, LYPLA2, MACF1, MAN1B1, MAN2A1, MAN2B1, MANBA, MANSC1, MAPK14, MAPRE1, MAT2A, MAT2B, MDH1, MDK, ME1, ME2, MELTF, MET, MGAT5, MIF, MINPP1, MME, MMP15, MSLN, MTAP, MUC13, MYDGF, MYG1, MYH14, MYL12A, NAA25, NAE1, NAGA, NAGK, NAGLU, NAMPT, NANS, NAP1L4, NAPRT, NARS1, NAXE, NCR3LG1, NCSTN, NDRG1, NECTIN1, NECTIN2, NECTIN3, NECTIN4, NEDD8, NEU1, NHEJ1, NHLRC2, NHLRC3, NIBAN2, NIF3L1, NIPSNAP3A, NISCH, NIT2, NLN, NME1, NPC2, NPEPL1, NPEPPS, NPLOC4, NPNT, NQO1, NRDC, NRP2, NSFL1C, NT5C2, NT5DC1, NTRK2, NUCB1, NUCKS1, NUDC, NUDCD1, NUDT14, NUDT21, NUDT5, NUMA1, NUP214, NUTF2, OLA1, OLFM4, OSBP, OTUB1, PA2G4, PABPC1, PABPC4, PAFAH1B1, PAFAH1B2, PAFAH1B3, PAIP1, PAK1, PALD1, PAM, PBDC1, PCBD1, PCDH1, PCSK9, PCYT2, PDCD10, PDCD6, PDCD6IP, PDIA4, PDIA5, PDXK, PEBP1, PEPD, PFAS, PFDN1, PFDN2, PFDN5, PFDN6, PGAM1, PGD, PGLS, PGM2, PGM2L1, PGM3, PGP, PICALM, PIR, PITPNB, PLA2G15, PLAUR, PLBD1, PLBD2, PLCB3, PLEC, PLOD1, PLOD3, PLPBP, PLS3, PLTP, PLXNA1, PLXNB1, PLXNB2, PM20D2, PNPO, PODXL2, POFUT1, POTEE, PPA1, PPA2, PPID, PPIL1, PPM1B, PPM1G, PPME1, PPP1CA, PPP1R7, PPP2CA, PPP2R1A, PPP2R2A, PPP3CA, PPP4C, PPP5C, PPP6C, PPP6R3, PPT1, PRCP, PRDX4, PRDX5, PREP, PRKACA, PRKAR2A, PRKCSH, PRMT1, PROCR, PRPS2, PRRC1, PRSS22, PRSS8, PSAP, PSAT1, PSMA1, PSMA2, PSMA3, PSMA4, PSMB1, PSMB2, PSMB6, PSMD2, PSMD3, PSMD6, PSMD7, PSMD8, PSME2, PSME3, PSPH, PTGES3, PTK7, PTMA, PTPA, PTPN11, PTPRD, PTPRF, PTPRG, PTPRK, PURA, PURB, PUS7, PVR, PYGB, PYGL, QARS1, QDPR, QPCT, QPRT, QSOX1, QSOX2, RAB1A, RAB6A, RABL6, RAC1, RACK1, RANBP3, RARS1, RBBP4, RBBP7, RBBP9, RBM8A, RCC2, REN, REXO2, RHOA, RIDA, RNASE1, RNASE4, RNASET2, RNH1, RNPEP, RO60, RPE, RPIA, RPL10A, RPN2, RPRD1B, RPS12, RPS15A, RPS20, RPS5, RRBP1, RRM2, RRP12, RSU1, S100A4, S100P, SAE1, SCRN1, SCYL2, SDC1, SDC4, SDF4, SDHA, SEC13, SEC23A, SEC23B, SEC23IP, SEC24C, SELENBP1, SELENOF, SEMA3A, SEMA4B, SEMA4C, SEMA4D, SEMA4G, SEMA6A, SEPHS1, SEPTIN2, SEPTIN7, SERPINB5, SERPINB6, SERPINE2, SERPINH1, SET, SF3A1, SF3A2, SF3A3, SF3B3, SFN, SFPQ, SGSH, SGTA, SIAE, SIL1, SKP1, SLC39A10, SLC3A2, SMOC1, SMOC2, SMPDL3A, SMS, SND1, SNRPF, SNRPN, SOD1, SOD2, SORD, SORT1, SPINT1, SPR, SPTAN1, SPTBN1, SRP9, SRPX2, SSB, SSBP1, ST13, ST14, ST6GAL1, STAG2, STARD10, STAU1, STC2, STK24, STRAP, STRN, SUMO2, SUPT16H, SYNCRIP, SYNE2, TARS1, TBCA, TCEA1, TCN1, TCP1, TES, TFG, TFRC, TGFBI, TGFBR3, THOP1, THUMPD1, TIMM13, TIMP1, TINAGL1, TIPRL, TK1, TKFC, TLN2, TMEM132A, TNFRSF1B, TNFRSF21, TNPO3, TP53I3, TPM1, TPM4, TPP1, TPP2, TPT1, TRIP10, TRIP11, TRNT1, TSN, TSNAX, TTLL12, TTN, TTN.1, TUBA1B, TUBA1C, TUBB4A, TWF2, TXNDC17, TXNDC5, TXNL1, TXNRD1, TXNRD2, TYRO3, U2AF2, UAP1, UBA2, UBA3, UBE2I, UBE2K, UBE2L3, UBE2M, UBE2N, UBE2V1, UBE2V2, UBLCP1, UBQLN1, UFC1, UGDH, UGGT1, UGP2, UROD, USP14, USP5, USP7, VASP, VBP1, VCL, VEGFA, VIL1, VPS26A, VPS35, VSNL1, WARS1, XPNPEP1, XPO1, XRCC5, XRN2, YARS1, YWHAG, ZFR</t>
   </si>
   <si>
     <t xml:space="preserve">1/2/4</t>
   </si>
   <si>
-    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_UC/HNPCC_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEA1, EIF3B, GSPT1, KTN1, SEMA5A, SEPTIN11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/2/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_UC/HCF_UC</t>
+    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_UC/SAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCT7, KRT78, LSM4, MTHFD1, RAB1B, RPLP2, RPS10, RPS19, RPS2</t>
   </si>
   <si>
     <t xml:space="preserve">1/3/4</t>
   </si>
   <si>
-    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_FPLC/HNPCC_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F10, PTGR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/3/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_FPLC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/4/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_2D_UC/HNPCC_UC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1R, C3, C4B, CLU, FBLN1, ITM2B, LTF, PLG, RTN4, SMPD1, VTN</t>
+    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_FPLC/SAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHSG, ARPC5L, F10, HNRNPA3, HNRNPH1, HSD17B10, SRP14</t>
   </si>
   <si>
     <t xml:space="preserve">2/3/4</t>
   </si>
   <si>
-    <t xml:space="preserve">DiFi_3D_UC/DiFi_3D_FPLC/HNPCC_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPN2, FSCN1, TNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/3/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_3D_UC/DiFi_3D_FPLC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/4/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_3D_UC/HNPCC_UC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FN1, GPC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3/4/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_3D_FPLC/HNPCC_UC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMB2</t>
+    <t xml:space="preserve">DiFi_3D_UC/DiFi_3D_FPLC/SAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOH, COL6A1</t>
   </si>
   <si>
     <t xml:space="preserve">1/2/3/4</t>
   </si>
   <si>
-    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_UC/DiFi_3D_FPLC/HNPCC_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAT2, ACO1, ACTC1, ACTR2, ACTR3, ADH5, AKR1A1, ALDH1A1, AP1G1, AP2B1, ARHGAP1, ARPC1A, ARPC1B, ARPC2, ARPC3, ARPC4, B4GALT1, CAND1, CAPN1, CAPZA2, CAPZB, CARS1, CCT5, CNDP2, COPB2, COTL1, CPPED1, DAG1, DDB1, DDX39B, DPP3, EEF1A1, EEF1G, ENO1, EPDR1, ERAP1, ERAP2, ERO1A, FKBP10, FKBP9, FUCA1, FUCA2, G6PD, GARS1, GBE1, GDI1, GLB1, GLG1, GNPDA2, GSTO1, HARS1, HSPA8, IDUA, ILF2, ILF3, IPO7, KARS1, KIF5B, KPNB1, LTA4H, LTBP4, MACF1, MAN2A1, ME1, MINPP1, NAMPT, NARS1, NCL, NIBAN2, NPC2, NPEPPS, NPM1, NT5C2, NUCB1, OLA1, PABPC1, PAM, PDIA4, PDIA6, PEBP1, PFN1, PGM2, PKM, PLEC, PLXNB2, PNP, PPIB, PPP3CA, PRDX4, PRDX6, PREP, PSMA6, PSMA7, PSMB3, PSMD6, PYGB, RNASET2, RNPEP, RO60, RPLP0, RPS15A, RPS27A, SDC4, SEC13, SEMA3A, SEPTIN2, SEPTIN7, SERPINB1, SERPINH1, SET, SNRPD1, SRPX2, TARS1, TLN1, TLN2, TP53I3, TPM1, TPM3, TSN, TUBA1A, TUBB, TUBB4B, UBA1, UGGT1, UROD, VCP, VPS35, WARS1, YWHAQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/2/3/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_UC/DiFi_3D_FPLC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/2/4/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_UC/HNPCC_UC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMB1, SOD3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/3/4/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_FPLC/HNPCC_UC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHSG, PLAU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/3/4/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_3D_UC/DiFi_3D_FPLC/HNPCC_UC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1B1, CD109, COL6A1, DPP4, LRP1, MAN2B2, PLOD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/2/3/4/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_UC/DiFi_3D_FPLC/HNPCC_UC/HCF_UC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTB, ACTN1, ACTN4, AGA, AGRN, ALAD, ALCAM, ALDOA, ALDOC, ANXA2, APLP2, APP, ARSA, ASAH1, ATRN, B4GAT1, BTD, C1QBP, CALR, CD44, CFB, CLN5, CLSTN1, CLTC, CORO1C, CREG1, CTBS, CTSA, CTSB, CTSC, CTSZ, DLD, DNASE2, DPP7, DPYSL2, ECM1, EEF2, EXT1, EXT2, EZR, FAH, FLNA, FLNB, GALNS, GAPDH, GAS6, GDI2, GGH, GNPDA1, GNPTG, GNS, GOT1, GOT2, GPC1, GPI, GRN, GSR, GSS, HEXA, HEXB, HSP90AA1, HSP90AB1, HSP90B1, HSPA5, HSPG2, IQGAP1, ISOC1, KRT1, KRT2, KRT9, LAMA3, LAMA5, LAMC1, LAMP1, LAMP2, LDHA, LDHB, LDLR, LGALS3, LGALS3BP, LGMN, LIPA, LMAN2, LMNA, MAN2B1, MANBA, MDH1, MDH2, MGAT5, MYH9, MYL6, NAGLU, NME1, NME2, NRP2, P4HB, PDIA3, PEPD, PGAM1, PGD, PLA2G15, PLBD2, PLOD1, PLOD3, PLS3, POTEE, PRCP, PRDX2, PRKCSH, PROCR, PSAP, PTK7, PTPRK, QSOX1, RPL10A, SERPINB6, SERPINE2, SERPINF1, SGSH, SIAE, SMPDL3A, SOD1, SOD2, SPTAN1, SPTBN1, STAT1, STC2, TALDO1, TGFBI, THBS1, TIMP1, TKT, TPI1, TPM4, TPP1, TUBA1B, TXN, TXNDC5, TXNRD1, VCL, WDR1, YWHAB, YWHAE, YWHAG, YWHAH, YWHAZ</t>
+    <t xml:space="preserve">DiFi_2D_UC/DiFi_3D_UC/DiFi_3D_FPLC/SAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABRACL, ACTB, ACTN4, ACTR3, AHCY, AHNAK, ALDOA, ALDOC, ANP32A, ANP32B, ANXA2, ARHGDIA, ARPC1B, ARPC2, ARPC4, ARPC5, ATIC, BLMH, BTF3, C1QBP, CALM1, CALR, CAP1, CAPG, CAPNS1, CAPZA2, CAPZB, CCT2, CCT6A, CCT8, CDC42, CFL1, CLIC1, CLTC, COTL1, DSP, ECH1, EEF1D, EEF1G, EEF2, EIF4A1, ENO1, FABP5, FLNA, G6PD, GANAB, GAPDH, GDI2, GGCT, GPI, GSTO1, GSTP1, HK1, HMGB1, HMGB2, HNRNPA1, HNRNPA2B1, HNRNPAB, HNRNPC, HNRNPF, HNRNPK, HNRNPU, HSP90AA1, HSP90AB1, HSP90B1, HSPA5, HSPA8, HSPA9, HSPD1, HSPE1, JUP, KRT1, KRT10, KRT18, KRT2, KRT8, KRT9, LCP1, LDHA, LDHB, LMNB1, MDH2, MYH9, MYL6, NACA, NASP, NCL, NME2, NPM1, P4HB, PAICS, PARK7, PCBP1, PCBP2, PCNA, PDIA3, PDIA6, PFN1, PGK1, PKM, PLS1, PNP, PPIA, PPIB, PRDX1, PRDX2, PRDX3, PRDX6, PRSS2, PSMA5, PSMA6, PSMA7, PSMB3, PSME1, PTBP1, RAB11B, RAN, RPL11, RPL12, RPL22, RPLP0, RPS27A, RPS28, RPS3, RPS7, RPSA, S100A11, S100A6, SERPINA1, SERPINB1, SERPINF1, SH3BGRL3, SNRPB2, SNRPD1, SNRPD2, SNRPD3, SNRPE, SNRPGP15, STAT1, STIP1, SUB1, TAGLN2, TALDO1, THBS1, TKT, TLN1, TPI1, TPM3, TPR, TUBA1A, TUBA4A, TUBB, TUBB4B, TXN, UBA1, UBE2D3, VCP, WDR1, XRCC6, YBX1, YWHAB, YWHAE, YWHAH, YWHAQ, YWHAZ</t>
   </si>
 </sst>
 </file>
@@ -638,7 +512,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>505</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3">
@@ -652,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -666,7 +540,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -680,7 +554,7 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6">
@@ -694,7 +568,7 @@
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -708,7 +582,7 @@
         <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>94</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8">
@@ -722,7 +596,7 @@
         <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -736,7 +610,7 @@
         <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -750,7 +624,7 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -764,7 +638,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -775,290 +649,66 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>836</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="n">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
